--- a/pa-temp-fix-system.com/php/shell/sp/target/excel/M6增投asin.xlsx
+++ b/pa-temp-fix-system.com/php/shell/sp/target/excel/M6增投asin.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
   <si>
     <t>channel</t>
   </si>
@@ -38,13 +38,13 @@
     <t>seller_id</t>
   </si>
   <si>
-    <t>keyword_id</t>
+    <t>campaign_id</t>
   </si>
   <si>
     <t>ad_group_id</t>
   </si>
   <si>
-    <t>search_term-可直接复制</t>
+    <t>keywordtext</t>
   </si>
   <si>
     <t>增投类型</t>
@@ -62,7 +62,7 @@
     <t>amazon</t>
   </si>
   <si>
-    <t>121195984049723</t>
+    <t>131494784731465</t>
   </si>
   <si>
     <t>51557465334438</t>
@@ -77,9 +77,6 @@
     <t/>
   </si>
   <si>
-    <t>58454565585335</t>
-  </si>
-  <si>
     <t>249764982385294</t>
   </si>
   <si>
@@ -95,7 +92,7 @@
     <t>amazon_ca_hood</t>
   </si>
   <si>
-    <t>511084918297364</t>
+    <t>346345307604386</t>
   </si>
   <si>
     <t>318298234868327</t>
@@ -107,7 +104,7 @@
     <t>amazon_ca_tuto</t>
   </si>
   <si>
-    <t>377649905012286</t>
+    <t>389591848098528</t>
   </si>
   <si>
     <t>512460314645757</t>
@@ -119,7 +116,7 @@
     <t>amazon_ca_tuc</t>
   </si>
   <si>
-    <t>274749273905245</t>
+    <t>266127362174204</t>
   </si>
   <si>
     <t>401456032237948</t>
@@ -131,7 +128,7 @@
     <t>amazon_us_kilo</t>
   </si>
   <si>
-    <t>507444032718952</t>
+    <t>395905308036394</t>
   </si>
   <si>
     <t>342152963088432</t>
@@ -146,7 +143,7 @@
     <t>amazon_ca_piccocasa</t>
   </si>
   <si>
-    <t>486065596065030</t>
+    <t>546347693505450</t>
   </si>
   <si>
     <t>417234802863998</t>
@@ -155,7 +152,7 @@
     <t>B0CWPC929Q</t>
   </si>
   <si>
-    <t>557036461745308</t>
+    <t>403262971940249</t>
   </si>
   <si>
     <t>419956778003173</t>
@@ -1335,7 +1332,10 @@
   <cols>
     <col min="1" max="2" width="9.23148148148148" style="1"/>
     <col min="3" max="3" width="17.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.23148148148148" style="1"/>
+    <col min="4" max="4" width="21.4444444444444" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="14.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1396,13 +1396,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -1426,7 +1426,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
@@ -1438,19 +1438,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>13</v>
@@ -1462,19 +1462,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>13</v>
@@ -1486,19 +1486,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -1513,16 +1513,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>13</v>
@@ -1540,13 +1540,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>13</v>
@@ -1570,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
@@ -1582,19 +1582,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
@@ -1612,13 +1612,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
@@ -1642,7 +1642,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>13</v>
